--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1024,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122462195</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91193</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svarvarbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587745</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6548748</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B2" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R2" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444321</v>
+        <v>122444314</v>
       </c>
       <c r="B3" t="n">
-        <v>105290</v>
+        <v>90231</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,27 +807,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587746</v>
+        <v>587737</v>
       </c>
       <c r="R3" t="n">
-        <v>6548720</v>
+        <v>6548752</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444314</v>
+        <v>122444320</v>
       </c>
       <c r="B4" t="n">
-        <v>90219</v>
+        <v>105303</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,30 +926,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587737</v>
+        <v>587569</v>
       </c>
       <c r="R4" t="n">
-        <v>6548752</v>
+        <v>6548702</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444321</v>
+        <v>122444314</v>
       </c>
       <c r="B2" t="n">
-        <v>105303</v>
+        <v>90235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587746</v>
+        <v>587737</v>
       </c>
       <c r="R2" t="n">
-        <v>6548720</v>
+        <v>6548752</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444314</v>
+        <v>122444320</v>
       </c>
       <c r="B3" t="n">
-        <v>90231</v>
+        <v>105308</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +810,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587737</v>
+        <v>587569</v>
       </c>
       <c r="R3" t="n">
-        <v>6548752</v>
+        <v>6548702</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B4" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R4" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91193</v>
+        <v>91198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444314</v>
+        <v>122444320</v>
       </c>
       <c r="B2" t="n">
-        <v>90235</v>
+        <v>105317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4189</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kamjordstjärna</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587737</v>
+        <v>587569</v>
       </c>
       <c r="R2" t="n">
-        <v>6548752</v>
+        <v>6548702</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B3" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,11 +803,6 @@
       </c>
       <c r="E3" t="n">
         <v>221144</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -838,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R3" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444321</v>
+        <v>122444314</v>
       </c>
       <c r="B4" t="n">
-        <v>105308</v>
+        <v>90240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,27 +913,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>4189</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587746</v>
+        <v>587737</v>
       </c>
       <c r="R4" t="n">
-        <v>6548720</v>
+        <v>6548752</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1014,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91198</v>
+        <v>91203</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122444320</v>
       </c>
       <c r="B2" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>221144</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -789,7 +794,7 @@
         <v>122444321</v>
       </c>
       <c r="B3" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,6 +808,11 @@
       </c>
       <c r="E3" t="n">
         <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -900,7 +910,7 @@
         <v>122444314</v>
       </c>
       <c r="B4" t="n">
-        <v>90240</v>
+        <v>90253</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,6 +924,11 @@
       </c>
       <c r="E4" t="n">
         <v>4189</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1014,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91203</v>
+        <v>91216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122444320</v>
       </c>
       <c r="B2" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444321</v>
+        <v>122444314</v>
       </c>
       <c r="B3" t="n">
-        <v>105330</v>
+        <v>90266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,27 +807,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587746</v>
+        <v>587737</v>
       </c>
       <c r="R3" t="n">
-        <v>6548720</v>
+        <v>6548752</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444314</v>
+        <v>122444321</v>
       </c>
       <c r="B4" t="n">
-        <v>90253</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,30 +926,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587737</v>
+        <v>587746</v>
       </c>
       <c r="R4" t="n">
-        <v>6548752</v>
+        <v>6548720</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91216</v>
+        <v>91229</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B2" t="n">
         <v>105343</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R2" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444321</v>
+        <v>122444320</v>
       </c>
       <c r="B4" t="n">
         <v>105343</v>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587746</v>
+        <v>587569</v>
       </c>
       <c r="R4" t="n">
-        <v>6548720</v>
+        <v>6548702</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444321</v>
+        <v>122444320</v>
       </c>
       <c r="B2" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587746</v>
+        <v>587569</v>
       </c>
       <c r="R2" t="n">
-        <v>6548720</v>
+        <v>6548702</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R4" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91229</v>
+        <v>91230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B2" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R2" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
         <v>122444314</v>
       </c>
       <c r="B3" t="n">
-        <v>90266</v>
+        <v>90267</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444321</v>
+        <v>122444320</v>
       </c>
       <c r="B4" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587746</v>
+        <v>587569</v>
       </c>
       <c r="R4" t="n">
-        <v>6548720</v>
+        <v>6548702</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91230</v>
+        <v>91231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444321</v>
+        <v>122444314</v>
       </c>
       <c r="B2" t="n">
-        <v>105347</v>
+        <v>90270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587746</v>
+        <v>587737</v>
       </c>
       <c r="R2" t="n">
-        <v>6548720</v>
+        <v>6548752</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444314</v>
+        <v>122444320</v>
       </c>
       <c r="B3" t="n">
-        <v>90267</v>
+        <v>105350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +810,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587737</v>
+        <v>587569</v>
       </c>
       <c r="R3" t="n">
-        <v>6548752</v>
+        <v>6548702</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B4" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R4" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91231</v>
+        <v>91234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444314</v>
+        <v>122444320</v>
       </c>
       <c r="B2" t="n">
-        <v>90270</v>
+        <v>105350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587737</v>
+        <v>587569</v>
       </c>
       <c r="R2" t="n">
-        <v>6548752</v>
+        <v>6548702</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444320</v>
+        <v>122444321</v>
       </c>
       <c r="B3" t="n">
         <v>105350</v>
@@ -838,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587569</v>
+        <v>587746</v>
       </c>
       <c r="R3" t="n">
-        <v>6548702</v>
+        <v>6548720</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444321</v>
+        <v>122444314</v>
       </c>
       <c r="B4" t="n">
-        <v>105350</v>
+        <v>90270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,27 +923,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587746</v>
+        <v>587737</v>
       </c>
       <c r="R4" t="n">
-        <v>6548720</v>
+        <v>6548752</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122444320</v>
       </c>
       <c r="B2" t="n">
-        <v>105350</v>
+        <v>105453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444321</v>
+        <v>122444314</v>
       </c>
       <c r="B3" t="n">
-        <v>105350</v>
+        <v>90373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,27 +807,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587746</v>
+        <v>587737</v>
       </c>
       <c r="R3" t="n">
-        <v>6548720</v>
+        <v>6548752</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122444314</v>
+        <v>122444321</v>
       </c>
       <c r="B4" t="n">
-        <v>90270</v>
+        <v>105453</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,30 +926,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587737</v>
+        <v>587746</v>
       </c>
       <c r="R4" t="n">
-        <v>6548752</v>
+        <v>6548720</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91234</v>
+        <v>91337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122444320</v>
       </c>
       <c r="B2" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>122444314</v>
       </c>
       <c r="B3" t="n">
-        <v>90373</v>
+        <v>90377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>122444321</v>
       </c>
       <c r="B4" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91337</v>
+        <v>91341</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122444320</v>
+        <v>122444314</v>
       </c>
       <c r="B2" t="n">
-        <v>105461</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587569</v>
+        <v>587737</v>
       </c>
       <c r="R2" t="n">
-        <v>6548702</v>
+        <v>6548752</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122444314</v>
+        <v>122444320</v>
       </c>
       <c r="B3" t="n">
-        <v>90377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,30 +800,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587737</v>
+        <v>587569</v>
       </c>
       <c r="R3" t="n">
-        <v>6548752</v>
+        <v>6548702</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,12 +903,7 @@
         <v>122444321</v>
       </c>
       <c r="B4" t="n">
-        <v>105461</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,12 +1014,7 @@
         <v>122462195</v>
       </c>
       <c r="B5" t="n">
-        <v>91341</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,6 +1023,11 @@
       </c>
       <c r="E5" t="n">
         <v>6040162</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 1149-2025 artfynd.xlsx
+++ b/artfynd/A 1149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122444314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122444320</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122444321</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,8 +1134,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122462195</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>